--- a/output/laminas_comunales/comunal_p_monto_aps_a_2021_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_p_monto_aps_a_2021_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C316"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>144684</v>
+        <v>156352.140625</v>
       </c>
     </row>
     <row r="3">
@@ -399,187 +399,4702 @@
         </is>
       </c>
       <c r="C3">
-        <v>143440.109375</v>
+        <v>155373.421875</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>Río Hurtado</t>
         </is>
       </c>
       <c r="C4">
-        <v>141355</v>
+        <v>154612.953125</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Río Hurtado</t>
+          <t>La Higuera</t>
         </is>
       </c>
       <c r="C5">
-        <v>140640.234375</v>
+        <v>152542.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="C6">
-        <v>136437.390625</v>
+        <v>150781.0625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="C7">
-        <v>135193.65625</v>
+        <v>148965.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4203</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="C8">
-        <v>134836.5</v>
+        <v>148746.625</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C9">
-        <v>132584.25</v>
+        <v>147914.390625</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C10">
-        <v>130350.0703125</v>
+        <v>146576.8125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="C11">
-        <v>128685.984375</v>
+        <v>145410.515625</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="C12">
-        <v>128394.46875</v>
+        <v>145125</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="C13">
-        <v>128145.25</v>
+        <v>144998.671875</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Andacollo</t>
+          <t>Canela</t>
         </is>
       </c>
       <c r="C14">
-        <v>125749.890625</v>
+        <v>144684</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>144667.40625</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>144278.234375</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>143873.078125</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>143440.109375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>143435.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>143343.4375</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>143017.65625</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>142877.421875</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>142717.8125</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>142614.8125</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>142025.703125</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>141941.3125</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>141701.84375</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>141563.3125</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>141355</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>140679.421875</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>140640.234375</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>139703.53125</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>139161.234375</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>138761.984375</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>138111.71875</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>138001.3125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>137884.4375</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>137805.84375</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>137651.5625</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>4201</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Illapel</t>
         </is>
       </c>
-      <c r="C15">
+      <c r="C40">
+        <v>137061.296875</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>136542.453125</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>136437.390625</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>136405.390625</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>135193.65625</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>135143.890625</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>134836.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>134669.6875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>134575.6875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>134116.796875</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>133157.046875</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>133087.8125</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>133029.34375</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>132668.25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>132584.25</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>132359.984375</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>131811.375</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>131715.71875</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>131308.40625</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>130885.4375</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>130653.1953125</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>130623.796875</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>130350.0703125</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>130291.0546875</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>130136.25</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>129883.890625</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>129850.546875</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>129171.0390625</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>128943.078125</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>128807.234375</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>128741.59375</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>128685.984375</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>128552.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>128394.46875</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>128145.25</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>127826.3984375</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>127383.015625</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>127098.8046875</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>127086.328125</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>126881.1015625</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>126508.6328125</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>126479.671875</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>126063.359375</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>125922.296875</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>125749.890625</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C85">
         <v>125662.234375</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>125136.9609375</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>124916.8515625</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>123999.0703125</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>123261.515625</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>122979.6875</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>121931.40625</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>121620.859375</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>120982.125</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>120396.1015625</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>120348.734375</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>120035.6328125</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>119795.984375</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>119463.4609375</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>118230.53125</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>117843.296875</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>117589.5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>117093.5390625</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>116335.2578125</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>113965.390625</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>113283.8359375</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>112274.140625</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>60.4790420532227</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>60.3537979125977</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>60.2766799926758</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>60.1960792541504</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>58.5829086303711</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>56.339469909668</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>55.8011054992676</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>55.6603775024414</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>55.5555572509766</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>55.2064628601074</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>54.8639907836914</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>54.2750930786133</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>54.1084518432617</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>53.3249702453613</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>53.3106117248535</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>53.2579193115234</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>53.114185333252</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>52.7253112792969</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>52.6303443908691</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>52.4564170837402</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>52.4409446716309</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>52.4044380187988</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>52.3631858825684</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>52.3323631286621</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>52.1327018737793</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>52.1298179626465</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>52.0538482666016</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>51.9645118713379</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>51.953125</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>51.6738510131836</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>51.5513114929199</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>51.4132919311523</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>51.2048187255859</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>51.1134910583496</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>51.1111106872559</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>50.8493156433105</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>50.7317085266113</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>50.6506309509277</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>50.3875961303711</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>50.2939262390137</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>50.2388191223145</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>50.2024307250977</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>50.1328392028809</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>50.1128044128418</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>50.0859260559082</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>50.0457153320312</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>49.9822616577149</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>49.9460639953613</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>49.934383392334</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>49.7235107421875</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>49.712459564209</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>49.6781425476074</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>49.5375137329102</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>49.3317832946777</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>49.2113571166992</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>49.1264839172363</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>49.0970649719238</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>49.0151519775391</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>49.0045928955078</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>48.8058166503906</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>48.7134742736816</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>48.7121429443359</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>48.6857147216797</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>48.1481475830078</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>48.0331268310547</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>47.9365081787109</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>47.8970489501953</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>47.7836227416992</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>47.6495742797851</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>47.4599494934082</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>47.3027610778809</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>47.1055603027344</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>47.0923080444336</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>47.0315284729004</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>47.0079803466797</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>47.0003700256348</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>46.7177238464355</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>46.5949821472168</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>46.3949851989746</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>46.383186340332</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>46.0153388977051</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>45.8839149475098</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>45.8816871643066</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>45.4716987609863</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>45.4365081787109</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>45.2998161315918</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>45.1317939758301</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>45.0704231262207</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>44.8628311157227</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>44.7072982788086</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>44.5205497741699</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>44.2289924621582</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>44.1441459655762</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>43.982494354248</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>43.6675643920898</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>43.4263687133789</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>42.8571434020996</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>42.633228302002</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>42.4603157043457</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>42.2303466796875</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>41.7808227539062</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>41.3978500366211</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>41.3125343322754</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>41.007194519043</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>40.9420280456543</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>40.3846168518066</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>40.2733955383301</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>39.3406600952149</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>39.0645942687988</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>38.7096786499023</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>38.461540222168</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>37.8076057434082</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>37.2793350219727</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>36.703296661377</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>35.9746437072754</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>35.365852355957</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>35.1209259033203</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>35.1203498840332</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>33.9670486450195</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>33.8340950012207</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>33.2310829162598</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>32.2799110412598</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>30.995475769043</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>30.8176097869873</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>30.7129802703857</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>30.566801071167</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>30.5334854125977</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>30.3773593902588</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>29.6296291351318</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>29.3406963348389</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>29.1338577270508</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>28.6883430480957</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>28.4839210510254</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>27.5449104309082</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>27.4463005065918</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>27.4447956085205</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>27.3972606658936</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>27.2300472259521</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>27.0021419525146</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>26.9541778564453</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>26.9146614074707</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>26.7295589447021</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>26.470588684082</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>26.1420478820801</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>26.0465106964111</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>25.9834365844727</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>25.0448837280273</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>24.9882564544678</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>24.8034172058105</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>24.5356788635254</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>24.202127456665</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>23.9336490631104</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>23.6036033630371</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>23.489933013916</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>23.3333339691162</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>23.2974910736084</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>23.0923690795898</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>22.7272720336914</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>22.6738929748535</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>22.5040473937988</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>22.3027610778809</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>22.2646560668945</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>22.1940212249756</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>22.176118850708</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>22.0877361297607</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>21.7864799499512</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>21.7723445892334</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>21.6790657043457</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>21.6472301483154</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>21.6019420623779</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>21.4549942016602</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>21.2707176208496</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>21.1764698028564</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>20.5771636962891</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>20.1492538452148</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>19.8436813354492</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>19.2971248626709</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>18.8760604858398</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>18.8187294006348</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>18.5574760437012</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>18.5435123443604</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>18.505859375</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>18.4126987457275</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>18.1140956878662</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>17.5925922393799</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>17.0938491821289</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>16.6763515472412</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>16.6177005767822</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>16.5827045440674</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>16.4811744689941</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>16.4319877624512</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>16.1850280761719</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>15.3702220916748</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>15.2249135971069</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>15.0222873687744</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>14.6822500228882</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>14.1502275466919</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>13.818977355957</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>13.5042734146118</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>13.2411336898804</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>13.204062461853</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>12.7936601638794</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>12.3829345703125</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>11.9702606201172</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>11.7112770080566</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>11.6045551300049</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>10.5142860412598</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>10.4673805236816</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>9.043502807617189</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>7.46904325485229</v>
       </c>
     </row>
   </sheetData>
